--- a/artfynd/A 4254-2024 artfynd.xlsx
+++ b/artfynd/A 4254-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4254-2024 artfynd.xlsx
+++ b/artfynd/A 4254-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114823880</v>
+        <v>114823820</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558786</v>
+        <v>558679</v>
       </c>
       <c r="R2" t="n">
-        <v>6371861</v>
+        <v>6371841</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114823853</v>
+        <v>114823827</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558801</v>
+        <v>558694</v>
       </c>
       <c r="R3" t="n">
-        <v>6371821</v>
+        <v>6371850</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114823827</v>
+        <v>114823853</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558694</v>
+        <v>558801</v>
       </c>
       <c r="R4" t="n">
-        <v>6371850</v>
+        <v>6371821</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1017,6 +1002,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114823880</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sönnerhult 2:8, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>558786</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6371861</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vena</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inge Jonsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inge Jonsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4254-2024 artfynd.xlsx
+++ b/artfynd/A 4254-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114823820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114823827</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114823853</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114823880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>